--- a/output/2026-10-03_21_Malesia_Pulau_Pinang_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-10-03_21_Malesia_Pulau_Pinang_Depolverazione_Trattamento_aria.xlsx
@@ -491,11 +491,9 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> oil mist collectors)</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+          <t xml:space="preserve"> oil mist collectors) [DUPLICATO — vedi anche: 2026-10-03_14_Malesia_Perlis_Depolverazione_Trattamento_aria.xlsx]</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>Azienda reale confermata tramite sito ufficiale, investpenang.gov.my (SMEs Directory) e jobstore.my. Engineering, manufacturer e installer di Air Pollution Control Systems per fumi chimici, polveri, fumi di saldatura, nebbia d'olio. Fondata nel 1996 (ex Jayatek Enterprise dal 1987), 51-100 dipendenti. Nota: e' produttore/installatore proprio di sistemi, non un distributore multimarca puro - valutare idoneita' come canale/partner Dupuy. Telefono ed email non reperiti da fonti verificabili (sito non accessibile in fetch, nessun contatto diretto trovato in ricerca).</t>
